--- a/Dataset/IT/ITAMed_Distribution_IT.xlsx
+++ b/Dataset/IT/ITAMed_Distribution_IT.xlsx
@@ -2989,7 +2989,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -4478,7 +4478,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -4589,7 +4589,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -4663,7 +4663,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">

--- a/Dataset/IT/ITAMed_Distribution_IT.xlsx
+++ b/Dataset/IT/ITAMed_Distribution_IT.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribuzione Immagini" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorie" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorie Immagine" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribuzione Tipo Domanda" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -43,7 +46,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +57,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +107,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5575,4 +5602,224 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Anno</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Case-Based</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge-Based</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Totale</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>% Case-Based</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>0.7928571428571428</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0.7285714285714285</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.7642857142857142</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.6214285714285714</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.7785714285714286</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.7642857142857142</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Totale</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>928</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>332</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.7365079365079366</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>